--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_DR.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_DR.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Raf9fbe2e174d4404"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R3deb56a1740b4dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R69972f3113354afe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rb21289560e2f438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Ra39dbe747366469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rca481fb299be4d59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rf63338a75e54440a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R96241ba1c47a45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rd4c7d88aef544665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R153193aea1ee4242"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Re51d53559f3241bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rffc0a8e8873447e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Re61538c23722491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rb3452be5614440a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R9f07a26da1e04c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R22991796364b43f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R67d679ffaa414522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rc67c2195201c4cf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rb59a22bad2734a76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rb898197e527045bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R22eae6b569ea4af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R60c3dde34b124975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R4b7dd8babfa44262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R45d26a7f03e44c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R87c20906ae67477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R82362a40fa334449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R34210ed8703748ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R103aa39a920c445a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R3d0b0e205f26438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rcbca2960142d4af3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R5832edb96e0743f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R930c12160b154a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Re9dddc99ac584a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R4f0cf82ea0c6425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rc1dfb5c0fd2941c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R73e4217521084aa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R0aac084b79cb4a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R512a38b0708748ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R1fd2b57c53524706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R6e6bebf281274449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R1c03b02e472f4047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R4e74f598bd4847a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Ra2fe2cdc97a840a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4354,6 +4355,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>アストリッド</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>冬の山？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
